--- a/resources/templates/standard/L1200-02.xlsx
+++ b/resources/templates/standard/L1200-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>금형 &amp; 치공구 이력카드</t>
   </si>
@@ -684,7 +687,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -693,7 +698,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -852,7 +857,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -872,7 +877,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
@@ -888,7 +893,7 @@
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
@@ -931,7 +936,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
@@ -947,11 +952,11 @@
       <c r="AE5" s="8"/>
       <c r="AF5" s="8"/>
       <c r="AG5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="7"/>
       <c r="AI5" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ5" s="7"/>
       <c r="AK5" s="7"/>
@@ -960,14 +965,14 @@
       <c r="AN5" s="7"/>
       <c r="AO5" s="7"/>
       <c r="AP5" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ5" s="7"/>
       <c r="AR5" s="7"/>
       <c r="AS5" s="7"/>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV5" s="7"/>
       <c r="AW5" s="7"/>
@@ -1035,7 +1040,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -1055,7 +1060,7 @@
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
@@ -1096,7 +1101,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1155,7 +1160,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1189,7 +1194,7 @@
       <c r="AE9" s="13"/>
       <c r="AF9" s="13"/>
       <c r="AG9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
@@ -1246,11 +1251,11 @@
       <c r="AE10" s="14"/>
       <c r="AF10" s="14"/>
       <c r="AG10" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH10" s="10"/>
       <c r="AI10" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="7"/>
@@ -1259,7 +1264,7 @@
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
       <c r="AP10" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7"/>
@@ -1270,7 +1275,7 @@
       <c r="AW10" s="7"/>
       <c r="AX10" s="7"/>
       <c r="AY10" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ10" s="7"/>
       <c r="BA10" s="7"/>
@@ -1364,7 +1369,7 @@
       <c r="AE12" s="14"/>
       <c r="AF12" s="14"/>
       <c r="AG12" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH12" s="15"/>
       <c r="AI12" s="9"/>
@@ -1421,7 +1426,7 @@
       <c r="AE13" s="14"/>
       <c r="AF13" s="14"/>
       <c r="AG13" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH13" s="15"/>
       <c r="AI13" s="9"/>
@@ -1478,7 +1483,7 @@
       <c r="AE14" s="14"/>
       <c r="AF14" s="14"/>
       <c r="AG14" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH14" s="15"/>
       <c r="AI14" s="9"/>
@@ -1535,7 +1540,7 @@
       <c r="AE15" s="14"/>
       <c r="AF15" s="14"/>
       <c r="AG15" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH15" s="15"/>
       <c r="AI15" s="9"/>
@@ -1592,7 +1597,7 @@
       <c r="AE16" s="14"/>
       <c r="AF16" s="14"/>
       <c r="AG16" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH16" s="15"/>
       <c r="AI16" s="9"/>
@@ -1649,7 +1654,7 @@
       <c r="AE17" s="14"/>
       <c r="AF17" s="14"/>
       <c r="AG17" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH17" s="15"/>
       <c r="AI17" s="9"/>
@@ -1706,7 +1711,7 @@
       <c r="AE18" s="14"/>
       <c r="AF18" s="14"/>
       <c r="AG18" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH18" s="15"/>
       <c r="AI18" s="9"/>
@@ -1763,7 +1768,7 @@
       <c r="AE19" s="14"/>
       <c r="AF19" s="14"/>
       <c r="AG19" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH19" s="15"/>
       <c r="AI19" s="9"/>
@@ -1820,7 +1825,7 @@
       <c r="AE20" s="14"/>
       <c r="AF20" s="14"/>
       <c r="AG20" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH20" s="15"/>
       <c r="AI20" s="9"/>
@@ -1877,7 +1882,7 @@
       <c r="AE21" s="14"/>
       <c r="AF21" s="14"/>
       <c r="AG21" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH21" s="15"/>
       <c r="AI21" s="9"/>
@@ -1934,7 +1939,7 @@
       <c r="AE22" s="14"/>
       <c r="AF22" s="14"/>
       <c r="AG22" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH22" s="15"/>
       <c r="AI22" s="9"/>
@@ -1991,7 +1996,7 @@
       <c r="AE23" s="14"/>
       <c r="AF23" s="14"/>
       <c r="AG23" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH23" s="15"/>
       <c r="AI23" s="9"/>
@@ -2048,7 +2053,7 @@
       <c r="AE24" s="14"/>
       <c r="AF24" s="14"/>
       <c r="AG24" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH24" s="15"/>
       <c r="AI24" s="9"/>
@@ -2105,7 +2110,7 @@
       <c r="AE25" s="14"/>
       <c r="AF25" s="14"/>
       <c r="AG25" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AH25" s="15"/>
       <c r="AI25" s="9"/>
@@ -2162,7 +2167,7 @@
       <c r="AE26" s="14"/>
       <c r="AF26" s="14"/>
       <c r="AG26" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH26" s="15"/>
       <c r="AI26" s="9"/>
@@ -2219,7 +2224,7 @@
       <c r="AE27" s="14"/>
       <c r="AF27" s="14"/>
       <c r="AG27" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH27" s="16"/>
       <c r="AI27" s="12"/>
@@ -2244,7 +2249,7 @@
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2271,7 +2276,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA28" s="5"/>
       <c r="AB28" s="5"/>
@@ -2328,7 +2333,7 @@
       <c r="X29" s="17"/>
       <c r="Y29" s="17"/>
       <c r="Z29" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA29" s="18"/>
       <c r="AB29" s="18"/>
